--- a/Student_Import_Template.xlsx
+++ b/Student_Import_Template.xlsx
@@ -8,67 +8,125 @@
   </bookViews>
   <sheets>
     <sheet name="Students" sheetId="1" r:id="rId1"/>
+    <sheet name="Instructions" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Students!$A$1:$R$1</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
-  <si>
-    <t>Student Name</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+  <si>
+    <t>* First Name</t>
+  </si>
+  <si>
+    <t>Middle Name</t>
+  </si>
+  <si>
+    <t>* Last Name</t>
+  </si>
+  <si>
+    <t>* Mobile Number</t>
+  </si>
+  <si>
+    <t>* Email Address</t>
   </si>
   <si>
     <t>PRN</t>
   </si>
   <si>
-    <t>Mobile</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Pramod bagade</t>
-  </si>
-  <si>
-    <t>pmb@gmail.com</t>
-  </si>
-  <si>
-    <t>student1</t>
-  </si>
-  <si>
-    <t>222222@gmail.com</t>
-  </si>
-  <si>
-    <t>student2</t>
-  </si>
-  <si>
-    <t>student3</t>
-  </si>
-  <si>
-    <t>student4</t>
-  </si>
-  <si>
-    <t>student5</t>
-  </si>
-  <si>
-    <t>student6</t>
-  </si>
-  <si>
-    <t>student7</t>
-  </si>
-  <si>
-    <t>student8</t>
-  </si>
-  <si>
-    <t>student9</t>
+    <t>Aadhaar Number</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Date of Birth</t>
+  </si>
+  <si>
+    <t>Parent Name</t>
+  </si>
+  <si>
+    <t>Parent Mobile</t>
+  </si>
+  <si>
+    <t>Parent Email</t>
+  </si>
+  <si>
+    <t>Permanent Address</t>
+  </si>
+  <si>
+    <t>Local Address</t>
+  </si>
+  <si>
+    <t>Emergency Contact Name</t>
+  </si>
+  <si>
+    <t>Emergency Contact Number</t>
+  </si>
+  <si>
+    <t>ABC ID</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>FacultyERP Student Import Instructions</t>
+  </si>
+  <si>
+    <t>1. Fields prefixed with * are mandatory.</t>
+  </si>
+  <si>
+    <t>2. Mobile Number must be unique.</t>
+  </si>
+  <si>
+    <t>3. Email Address must be unique.</t>
+  </si>
+  <si>
+    <t>4. PRN is optional during admission and can be updated later.</t>
+  </si>
+  <si>
+    <t>5. Aadhaar Number is optional.</t>
+  </si>
+  <si>
+    <t>6. Department, Course, Semester, Division and Academic Year are taken from the Student Master screen.</t>
+  </si>
+  <si>
+    <t>7. Do not modify the column headers.</t>
+  </si>
+  <si>
+    <t>Amit</t>
+  </si>
+  <si>
+    <t>Patil</t>
+  </si>
+  <si>
+    <t>Sneha</t>
+  </si>
+  <si>
+    <t>Joshi</t>
+  </si>
+  <si>
+    <t>sneha@test.com</t>
+  </si>
+  <si>
+    <t>amit@test.com</t>
+  </si>
+  <si>
+    <t>PRN1001</t>
+  </si>
+  <si>
+    <t>PRN1002</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -79,6 +137,12 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -90,15 +154,20 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -106,15 +175,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -415,13 +502,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:R6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="30" customWidth="1"/>
+    <col min="1" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="25" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="30" customWidth="1"/>
+    <col min="13" max="14" width="40" customWidth="1"/>
+    <col min="15" max="15" width="25" customWidth="1"/>
+    <col min="16" max="17" width="22" customWidth="1"/>
+    <col min="18" max="18" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -434,160 +534,151 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2">
-        <v>111111</v>
-      </c>
-      <c r="C2">
-        <v>1111111111</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2">
+        <v>9876543210</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
-        <v>222222</v>
-      </c>
-      <c r="C3">
-        <v>2222222222</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3">
+        <v>9876543211</v>
+      </c>
+      <c r="E3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="E6" s="3"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:R1"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="120" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>222222</v>
-      </c>
-      <c r="C4">
-        <v>2222222222</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>222222</v>
-      </c>
-      <c r="C5">
-        <v>2222222222</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>222222</v>
-      </c>
-      <c r="C6">
-        <v>2222222222</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7">
-        <v>222222</v>
-      </c>
-      <c r="C7">
-        <v>2222222222</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8">
-        <v>222222</v>
-      </c>
-      <c r="C8">
-        <v>2222222222</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9">
-        <v>222222</v>
-      </c>
-      <c r="C9">
-        <v>2222222222</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10">
-        <v>222222</v>
-      </c>
-      <c r="C10">
-        <v>2222222222</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11">
-        <v>222222</v>
-      </c>
-      <c r="C11">
-        <v>2222222222</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1"/>
-    <hyperlink ref="D3" r:id="rId2"/>
-    <hyperlink ref="D4" r:id="rId3"/>
-    <hyperlink ref="D5" r:id="rId4"/>
-    <hyperlink ref="D6" r:id="rId5"/>
-    <hyperlink ref="D7" r:id="rId6"/>
-    <hyperlink ref="D8" r:id="rId7"/>
-    <hyperlink ref="D9" r:id="rId8"/>
-    <hyperlink ref="D10" r:id="rId9"/>
-    <hyperlink ref="D11" r:id="rId10"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Student_Import_Template.xlsx
+++ b/Student_Import_Template.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="181">
   <si>
     <t>* First Name</t>
   </si>
@@ -98,18 +98,6 @@
     <t>7. Do not modify the column headers.</t>
   </si>
   <si>
-    <t>Amit</t>
-  </si>
-  <si>
-    <t>Patil</t>
-  </si>
-  <si>
-    <t>Sneha</t>
-  </si>
-  <si>
-    <t>Joshi</t>
-  </si>
-  <si>
     <t>sneha@test.com</t>
   </si>
   <si>
@@ -120,6 +108,459 @@
   </si>
   <si>
     <t>PRN1002</t>
+  </si>
+  <si>
+    <t>ADSUL</t>
+  </si>
+  <si>
+    <t>ATHARVA</t>
+  </si>
+  <si>
+    <t>CHANDRAKANT</t>
+  </si>
+  <si>
+    <t>AGRE</t>
+  </si>
+  <si>
+    <t>NINAD</t>
+  </si>
+  <si>
+    <t>DHANRAJ</t>
+  </si>
+  <si>
+    <t>AKASH</t>
+  </si>
+  <si>
+    <t>JIVAN</t>
+  </si>
+  <si>
+    <t>BHOSALE</t>
+  </si>
+  <si>
+    <t>AMOL</t>
+  </si>
+  <si>
+    <t>ANIL</t>
+  </si>
+  <si>
+    <t>BORATE</t>
+  </si>
+  <si>
+    <t>ANKUSHKAR</t>
+  </si>
+  <si>
+    <t>SHRUTI</t>
+  </si>
+  <si>
+    <t>SACHIN</t>
+  </si>
+  <si>
+    <t>ARJUN</t>
+  </si>
+  <si>
+    <t>KESHAV</t>
+  </si>
+  <si>
+    <t>VITTHAL</t>
+  </si>
+  <si>
+    <t>BHAGYWANT</t>
+  </si>
+  <si>
+    <t>AKSHAY</t>
+  </si>
+  <si>
+    <t>SUNIL</t>
+  </si>
+  <si>
+    <t>BHUMKAR</t>
+  </si>
+  <si>
+    <t>SARTHAK</t>
+  </si>
+  <si>
+    <t>SOMNATH</t>
+  </si>
+  <si>
+    <t>BIRMANE</t>
+  </si>
+  <si>
+    <t>VEDANT</t>
+  </si>
+  <si>
+    <t>PRAVIN</t>
+  </si>
+  <si>
+    <t>CHAUDHARI</t>
+  </si>
+  <si>
+    <t>PIYUSH</t>
+  </si>
+  <si>
+    <t>KISHOR</t>
+  </si>
+  <si>
+    <t>DEVESH</t>
+  </si>
+  <si>
+    <t>SATISH</t>
+  </si>
+  <si>
+    <t>MHASKE</t>
+  </si>
+  <si>
+    <t>DIGHULE</t>
+  </si>
+  <si>
+    <t>NILESH</t>
+  </si>
+  <si>
+    <t>DIVYA</t>
+  </si>
+  <si>
+    <t>ASHOK</t>
+  </si>
+  <si>
+    <t>GANBOTE</t>
+  </si>
+  <si>
+    <t>DIXIT</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>GADEKAR</t>
+  </si>
+  <si>
+    <t>PAYAL</t>
+  </si>
+  <si>
+    <t>VIJAY</t>
+  </si>
+  <si>
+    <t>GADHE</t>
+  </si>
+  <si>
+    <t>MRUDUL</t>
+  </si>
+  <si>
+    <t>GOKUL</t>
+  </si>
+  <si>
+    <t>GUPTA</t>
+  </si>
+  <si>
+    <t>PINKY</t>
+  </si>
+  <si>
+    <t>RAMPRASAD</t>
+  </si>
+  <si>
+    <t>HAGARE</t>
+  </si>
+  <si>
+    <t>SANIKA</t>
+  </si>
+  <si>
+    <t>PRADIP</t>
+  </si>
+  <si>
+    <t>HEDAU</t>
+  </si>
+  <si>
+    <t>SMIT</t>
+  </si>
+  <si>
+    <t>PRAKASH</t>
+  </si>
+  <si>
+    <t>JADHAV</t>
+  </si>
+  <si>
+    <t>HARSH</t>
+  </si>
+  <si>
+    <t>PARTH</t>
+  </si>
+  <si>
+    <t>BALASAHEB</t>
+  </si>
+  <si>
+    <t>JAGDALE</t>
+  </si>
+  <si>
+    <t>ADITYA</t>
+  </si>
+  <si>
+    <t>KALYAN</t>
+  </si>
+  <si>
+    <t>JAGTAP</t>
+  </si>
+  <si>
+    <t>ZUMBER</t>
+  </si>
+  <si>
+    <t>KADAM</t>
+  </si>
+  <si>
+    <t>ARYAN</t>
+  </si>
+  <si>
+    <t>SHYAMSUNDAR</t>
+  </si>
+  <si>
+    <t>KAHANE</t>
+  </si>
+  <si>
+    <t>MACHHINDRA</t>
+  </si>
+  <si>
+    <t>KAMBLE</t>
+  </si>
+  <si>
+    <t>SAKSHI</t>
+  </si>
+  <si>
+    <t>SANJAY</t>
+  </si>
+  <si>
+    <t>KOSHIMKAR</t>
+  </si>
+  <si>
+    <t>YASH</t>
+  </si>
+  <si>
+    <t>KOTHALE</t>
+  </si>
+  <si>
+    <t>KAVERI</t>
+  </si>
+  <si>
+    <t>BALNATH</t>
+  </si>
+  <si>
+    <t>KOUNDALKAR</t>
+  </si>
+  <si>
+    <t>SHREEYASH</t>
+  </si>
+  <si>
+    <t>MOTAPPA</t>
+  </si>
+  <si>
+    <t>KULKARNI</t>
+  </si>
+  <si>
+    <t>SOUNDARYA</t>
+  </si>
+  <si>
+    <t>UMAKANT</t>
+  </si>
+  <si>
+    <t>LOKESH</t>
+  </si>
+  <si>
+    <t>BENDRE</t>
+  </si>
+  <si>
+    <t>MANE</t>
+  </si>
+  <si>
+    <t>VIKAS</t>
+  </si>
+  <si>
+    <t>POPAT</t>
+  </si>
+  <si>
+    <t>MOHITE</t>
+  </si>
+  <si>
+    <t>YUGANDHAR</t>
+  </si>
+  <si>
+    <t>DHANAJI</t>
+  </si>
+  <si>
+    <t>MUTKULE</t>
+  </si>
+  <si>
+    <t>SOHAM</t>
+  </si>
+  <si>
+    <t>SANTOSH</t>
+  </si>
+  <si>
+    <t>PADWAL</t>
+  </si>
+  <si>
+    <t>SANKALP</t>
+  </si>
+  <si>
+    <t>YASHAVANT</t>
+  </si>
+  <si>
+    <t>PATHARE</t>
+  </si>
+  <si>
+    <t>VISHWANATH</t>
+  </si>
+  <si>
+    <t>PATIL</t>
+  </si>
+  <si>
+    <t>VILAS</t>
+  </si>
+  <si>
+    <t>PHADATARE</t>
+  </si>
+  <si>
+    <t>SHIVANI</t>
+  </si>
+  <si>
+    <t>PHATE</t>
+  </si>
+  <si>
+    <t>ADESH</t>
+  </si>
+  <si>
+    <t>SAMBHAJI</t>
+  </si>
+  <si>
+    <t>PRATHAMESH</t>
+  </si>
+  <si>
+    <t>MORE</t>
+  </si>
+  <si>
+    <t>PRATHMESH</t>
+  </si>
+  <si>
+    <t>RAJESH</t>
+  </si>
+  <si>
+    <t>RANGOLE</t>
+  </si>
+  <si>
+    <t>SANSKAR</t>
+  </si>
+  <si>
+    <t>RATHOD</t>
+  </si>
+  <si>
+    <t>AAKROSH</t>
+  </si>
+  <si>
+    <t>BALAJI</t>
+  </si>
+  <si>
+    <t>SHIVDHARMAVIRSINGH</t>
+  </si>
+  <si>
+    <t>P.</t>
+  </si>
+  <si>
+    <t>RIDDHI</t>
+  </si>
+  <si>
+    <t>ROHIT</t>
+  </si>
+  <si>
+    <t>PATANKAR</t>
+  </si>
+  <si>
+    <t>SALUNKE</t>
+  </si>
+  <si>
+    <t>SAMARTH</t>
+  </si>
+  <si>
+    <t>SHAH</t>
+  </si>
+  <si>
+    <t>SOHAIL</t>
+  </si>
+  <si>
+    <t>RAJU</t>
+  </si>
+  <si>
+    <t>SHARMA</t>
+  </si>
+  <si>
+    <t>SANGAM</t>
+  </si>
+  <si>
+    <t>SHELAR</t>
+  </si>
+  <si>
+    <t>AJAY</t>
+  </si>
+  <si>
+    <t>NITIN</t>
+  </si>
+  <si>
+    <t>SOMASE</t>
+  </si>
+  <si>
+    <t>GANPATI</t>
+  </si>
+  <si>
+    <t>SUBHASHCHANDRA</t>
+  </si>
+  <si>
+    <t>GOVINDAN</t>
+  </si>
+  <si>
+    <t>SUDKE</t>
+  </si>
+  <si>
+    <t>MANJUSHREE</t>
+  </si>
+  <si>
+    <t>RAMCHANDRA</t>
+  </si>
+  <si>
+    <t>TALEKAR</t>
+  </si>
+  <si>
+    <t>OM</t>
+  </si>
+  <si>
+    <t>NAMADEV</t>
+  </si>
+  <si>
+    <t>TAWADE</t>
+  </si>
+  <si>
+    <t>WAGHCHAURE</t>
+  </si>
+  <si>
+    <t>BHUSHAN</t>
+  </si>
+  <si>
+    <t>DEVRAM</t>
+  </si>
+  <si>
+    <t>WANKHADE</t>
+  </si>
+  <si>
+    <t>PRAJWAL</t>
+  </si>
+  <si>
+    <t>WARADE</t>
+  </si>
+  <si>
+    <t>SRUJAL</t>
+  </si>
+  <si>
+    <t>YEWALE</t>
+  </si>
+  <si>
+    <t>SHWET</t>
+  </si>
+  <si>
+    <t>SANJEEV</t>
   </si>
 </sst>
 </file>
@@ -502,7 +943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="20" customWidth="1"/>
@@ -579,46 +1020,667 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2">
         <v>9876543210</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D3">
         <v>9876543211</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
       <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>104</v>
+      </c>
+      <c r="B30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>107</v>
+      </c>
+      <c r="B31" t="s">
+        <v>108</v>
+      </c>
+      <c r="C31" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>110</v>
+      </c>
+      <c r="B32" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>113</v>
+      </c>
+      <c r="B33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" t="s">
+        <v>116</v>
+      </c>
+      <c r="C34" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>118</v>
+      </c>
+      <c r="B35" t="s">
+        <v>119</v>
+      </c>
+      <c r="C35" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>121</v>
+      </c>
+      <c r="B36" t="s">
+        <v>122</v>
+      </c>
+      <c r="C36" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>124</v>
+      </c>
+      <c r="B37" t="s">
+        <v>125</v>
+      </c>
+      <c r="C37" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>129</v>
+      </c>
+      <c r="B39" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>131</v>
+      </c>
+      <c r="B40" t="s">
+        <v>132</v>
+      </c>
+      <c r="C40" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>133</v>
+      </c>
+      <c r="B41" t="s">
+        <v>134</v>
+      </c>
+      <c r="C41" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>136</v>
+      </c>
+      <c r="B42" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>138</v>
+      </c>
+      <c r="B43" t="s">
+        <v>139</v>
+      </c>
+      <c r="C43" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>140</v>
+      </c>
+      <c r="B44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>142</v>
+      </c>
+      <c r="B45" t="s">
+        <v>143</v>
+      </c>
+      <c r="C45" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>142</v>
+      </c>
+      <c r="B46" t="s">
+        <v>145</v>
+      </c>
+      <c r="C46" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>147</v>
+      </c>
+      <c r="B47" t="s">
+        <v>148</v>
+      </c>
+      <c r="C47" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>150</v>
+      </c>
+      <c r="B48" t="s">
+        <v>151</v>
+      </c>
+      <c r="C48" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>152</v>
+      </c>
+      <c r="B49" t="s">
+        <v>153</v>
+      </c>
+      <c r="C49" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>155</v>
+      </c>
+      <c r="B50" t="s">
+        <v>156</v>
+      </c>
+      <c r="C50" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>157</v>
+      </c>
+      <c r="B51" t="s">
+        <v>158</v>
+      </c>
+      <c r="C51" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>160</v>
+      </c>
+      <c r="B52" t="s">
+        <v>45</v>
+      </c>
+      <c r="C52" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>162</v>
+      </c>
+      <c r="B53" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>164</v>
+      </c>
+      <c r="B54" t="s">
+        <v>165</v>
+      </c>
+      <c r="C54" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>167</v>
+      </c>
+      <c r="B55" t="s">
+        <v>168</v>
+      </c>
+      <c r="C55" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>170</v>
+      </c>
+      <c r="B56" t="s">
+        <v>148</v>
+      </c>
+      <c r="C56" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>171</v>
+      </c>
+      <c r="B57" t="s">
+        <v>172</v>
+      </c>
+      <c r="C57" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>174</v>
+      </c>
+      <c r="B58" t="s">
+        <v>175</v>
+      </c>
+      <c r="C58" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>176</v>
+      </c>
+      <c r="B59" t="s">
+        <v>177</v>
+      </c>
+      <c r="C59" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>178</v>
+      </c>
+      <c r="B60" t="s">
+        <v>179</v>
+      </c>
+      <c r="C60" t="s">
+        <v>180</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:R1"/>
